--- a/ShotCharts/shot_zones_2025_26.xlsx
+++ b/ShotCharts/shot_zones_2025_26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="526">
   <si>
     <t>Player</t>
   </si>
@@ -1577,6 +1577,21 @@
   </si>
   <si>
     <t>Trey Jemison</t>
+  </si>
+  <si>
+    <t>A.J. Green</t>
+  </si>
+  <si>
+    <t>Nicolas Claxton</t>
+  </si>
+  <si>
+    <t>Alexandre Sarr</t>
+  </si>
+  <si>
+    <t>AJ Lawson</t>
+  </si>
+  <si>
+    <t>Carlton Carrington</t>
   </si>
 </sst>
 </file>
@@ -1934,7 +1949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V500"/>
+  <dimension ref="A1:V505"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -35937,6 +35952,346 @@
         <v>0</v>
       </c>
     </row>
+    <row r="501" spans="1:22">
+      <c r="A501" t="s">
+        <v>521</v>
+      </c>
+      <c r="B501">
+        <v>417</v>
+      </c>
+      <c r="C501">
+        <v>0.0312</v>
+      </c>
+      <c r="D501">
+        <v>13</v>
+      </c>
+      <c r="E501">
+        <v>8</v>
+      </c>
+      <c r="F501">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="G501">
+        <v>0.0312</v>
+      </c>
+      <c r="H501">
+        <v>13</v>
+      </c>
+      <c r="I501">
+        <v>8</v>
+      </c>
+      <c r="J501">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="K501">
+        <v>0.0408</v>
+      </c>
+      <c r="L501">
+        <v>17</v>
+      </c>
+      <c r="M501">
+        <v>5</v>
+      </c>
+      <c r="N501">
+        <v>0.2941</v>
+      </c>
+      <c r="O501">
+        <v>0.271</v>
+      </c>
+      <c r="P501">
+        <v>113</v>
+      </c>
+      <c r="Q501">
+        <v>58</v>
+      </c>
+      <c r="R501">
+        <v>0.5133</v>
+      </c>
+      <c r="S501">
+        <v>0.6259</v>
+      </c>
+      <c r="T501">
+        <v>261</v>
+      </c>
+      <c r="U501">
+        <v>101</v>
+      </c>
+      <c r="V501">
+        <v>0.387</v>
+      </c>
+    </row>
+    <row r="502" spans="1:22">
+      <c r="A502" t="s">
+        <v>522</v>
+      </c>
+      <c r="B502">
+        <v>463</v>
+      </c>
+      <c r="C502">
+        <v>0.6069</v>
+      </c>
+      <c r="D502">
+        <v>281</v>
+      </c>
+      <c r="E502">
+        <v>199</v>
+      </c>
+      <c r="F502">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="G502">
+        <v>0.3089</v>
+      </c>
+      <c r="H502">
+        <v>143</v>
+      </c>
+      <c r="I502">
+        <v>60</v>
+      </c>
+      <c r="J502">
+        <v>0.4196</v>
+      </c>
+      <c r="K502">
+        <v>0.0497</v>
+      </c>
+      <c r="L502">
+        <v>23</v>
+      </c>
+      <c r="M502">
+        <v>12</v>
+      </c>
+      <c r="N502">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="O502">
+        <v>0.0022</v>
+      </c>
+      <c r="P502">
+        <v>1</v>
+      </c>
+      <c r="Q502">
+        <v>0</v>
+      </c>
+      <c r="R502">
+        <v>0</v>
+      </c>
+      <c r="S502">
+        <v>0.0324</v>
+      </c>
+      <c r="T502">
+        <v>15</v>
+      </c>
+      <c r="U502">
+        <v>3</v>
+      </c>
+      <c r="V502">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="503" spans="1:22">
+      <c r="A503" t="s">
+        <v>523</v>
+      </c>
+      <c r="B503">
+        <v>575</v>
+      </c>
+      <c r="C503">
+        <v>0.3652</v>
+      </c>
+      <c r="D503">
+        <v>210</v>
+      </c>
+      <c r="E503">
+        <v>151</v>
+      </c>
+      <c r="F503">
+        <v>0.719</v>
+      </c>
+      <c r="G503">
+        <v>0.3322</v>
+      </c>
+      <c r="H503">
+        <v>191</v>
+      </c>
+      <c r="I503">
+        <v>76</v>
+      </c>
+      <c r="J503">
+        <v>0.3979</v>
+      </c>
+      <c r="K503">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="L503">
+        <v>55</v>
+      </c>
+      <c r="M503">
+        <v>18</v>
+      </c>
+      <c r="N503">
+        <v>0.3273</v>
+      </c>
+      <c r="O503">
+        <v>0.0157</v>
+      </c>
+      <c r="P503">
+        <v>9</v>
+      </c>
+      <c r="Q503">
+        <v>3</v>
+      </c>
+      <c r="R503">
+        <v>0.3333</v>
+      </c>
+      <c r="S503">
+        <v>0.1913</v>
+      </c>
+      <c r="T503">
+        <v>110</v>
+      </c>
+      <c r="U503">
+        <v>37</v>
+      </c>
+      <c r="V503">
+        <v>0.3364</v>
+      </c>
+    </row>
+    <row r="504" spans="1:22">
+      <c r="A504" t="s">
+        <v>524</v>
+      </c>
+      <c r="B504">
+        <v>41</v>
+      </c>
+      <c r="C504">
+        <v>0.3415</v>
+      </c>
+      <c r="D504">
+        <v>14</v>
+      </c>
+      <c r="E504">
+        <v>7</v>
+      </c>
+      <c r="F504">
+        <v>0.5</v>
+      </c>
+      <c r="G504">
+        <v>0.122</v>
+      </c>
+      <c r="H504">
+        <v>5</v>
+      </c>
+      <c r="I504">
+        <v>1</v>
+      </c>
+      <c r="J504">
+        <v>0.2</v>
+      </c>
+      <c r="K504">
+        <v>0</v>
+      </c>
+      <c r="L504">
+        <v>0</v>
+      </c>
+      <c r="M504">
+        <v>0</v>
+      </c>
+      <c r="N504">
+        <v>0</v>
+      </c>
+      <c r="O504">
+        <v>0.3659</v>
+      </c>
+      <c r="P504">
+        <v>15</v>
+      </c>
+      <c r="Q504">
+        <v>5</v>
+      </c>
+      <c r="R504">
+        <v>0.3333</v>
+      </c>
+      <c r="S504">
+        <v>0.1707</v>
+      </c>
+      <c r="T504">
+        <v>7</v>
+      </c>
+      <c r="U504">
+        <v>3</v>
+      </c>
+      <c r="V504">
+        <v>0.4286</v>
+      </c>
+    </row>
+    <row r="505" spans="1:22">
+      <c r="A505" t="s">
+        <v>525</v>
+      </c>
+      <c r="B505">
+        <v>507</v>
+      </c>
+      <c r="C505">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="D505">
+        <v>36</v>
+      </c>
+      <c r="E505">
+        <v>16</v>
+      </c>
+      <c r="F505">
+        <v>0.4444</v>
+      </c>
+      <c r="G505">
+        <v>0.1321</v>
+      </c>
+      <c r="H505">
+        <v>67</v>
+      </c>
+      <c r="I505">
+        <v>23</v>
+      </c>
+      <c r="J505">
+        <v>0.3433</v>
+      </c>
+      <c r="K505">
+        <v>0.2012</v>
+      </c>
+      <c r="L505">
+        <v>102</v>
+      </c>
+      <c r="M505">
+        <v>45</v>
+      </c>
+      <c r="N505">
+        <v>0.4412</v>
+      </c>
+      <c r="O505">
+        <v>0.0769</v>
+      </c>
+      <c r="P505">
+        <v>39</v>
+      </c>
+      <c r="Q505">
+        <v>14</v>
+      </c>
+      <c r="R505">
+        <v>0.359</v>
+      </c>
+      <c r="S505">
+        <v>0.5187</v>
+      </c>
+      <c r="T505">
+        <v>263</v>
+      </c>
+      <c r="U505">
+        <v>101</v>
+      </c>
+      <c r="V505">
+        <v>0.384</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ShotCharts/shot_zones_2025_26.xlsx
+++ b/ShotCharts/shot_zones_2025_26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t>Player</t>
   </si>
@@ -380,6 +380,156 @@
   </si>
   <si>
     <t>Jock Landale</t>
+  </si>
+  <si>
+    <t>Quinten Post</t>
+  </si>
+  <si>
+    <t>Herbert Jones</t>
+  </si>
+  <si>
+    <t>Sam Hauser</t>
+  </si>
+  <si>
+    <t>Dereck Lively II</t>
+  </si>
+  <si>
+    <t>Spencer Jones</t>
+  </si>
+  <si>
+    <t>Ryan Dunn</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Collin Murray-Boyles</t>
+  </si>
+  <si>
+    <t>Aaron Wiggins</t>
+  </si>
+  <si>
+    <t>Kyle Filipowski</t>
+  </si>
+  <si>
+    <t>Keyonte George</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Jay Huff</t>
+  </si>
+  <si>
+    <t>James Harden</t>
+  </si>
+  <si>
+    <t>Kenrich Williams</t>
+  </si>
+  <si>
+    <t>Naji Marshall</t>
+  </si>
+  <si>
+    <t>Vince Williams Jr.</t>
+  </si>
+  <si>
+    <t>Baylor Scheierman</t>
+  </si>
+  <si>
+    <t>Derik Queen</t>
+  </si>
+  <si>
+    <t>Myron Gardner</t>
+  </si>
+  <si>
+    <t>Kris Murray</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Jaylen Wells</t>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Marcus Sasser</t>
+  </si>
+  <si>
+    <t>Brice Sensabaugh</t>
+  </si>
+  <si>
+    <t>Vit Krejci</t>
+  </si>
+  <si>
+    <t>Mitchell Robinson</t>
+  </si>
+  <si>
+    <t>Nae'Qwan Tomlin</t>
+  </si>
+  <si>
+    <t>Chris Boucher</t>
+  </si>
+  <si>
+    <t>Dwight Powell</t>
+  </si>
+  <si>
+    <t>Adem Bona</t>
+  </si>
+  <si>
+    <t>Devin Carter</t>
+  </si>
+  <si>
+    <t>Dru Smith</t>
+  </si>
+  <si>
+    <t>Will Richard</t>
+  </si>
+  <si>
+    <t>Kelly Oubre Jr.</t>
+  </si>
+  <si>
+    <t>Davion Mitchell</t>
+  </si>
+  <si>
+    <t>Dean Wade</t>
+  </si>
+  <si>
+    <t>Svi Mykhailiuk</t>
+  </si>
+  <si>
+    <t>Daniss Jenkins</t>
+  </si>
+  <si>
+    <t>Craig Porter</t>
+  </si>
+  <si>
+    <t>Cooper Flagg</t>
+  </si>
+  <si>
+    <t>Dominick Barlow</t>
+  </si>
+  <si>
+    <t>Johnny Furphy</t>
+  </si>
+  <si>
+    <t>Olivier-Maxence Prosper</t>
+  </si>
+  <si>
+    <t>Jaxson Hayes</t>
+  </si>
+  <si>
+    <t>Isaiah Joe</t>
+  </si>
+  <si>
+    <t>Jabari Walker</t>
+  </si>
+  <si>
+    <t>Max Christie</t>
+  </si>
+  <si>
+    <t>Ryan Kalkbrenner</t>
   </si>
 </sst>
 </file>
@@ -737,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:V151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -7608,6 +7758,3406 @@
         <v>0.3723</v>
       </c>
     </row>
+    <row r="102" spans="1:22">
+      <c r="A102" t="s">
+        <v>122</v>
+      </c>
+      <c r="B102">
+        <v>439</v>
+      </c>
+      <c r="C102">
+        <v>0.1777</v>
+      </c>
+      <c r="D102">
+        <v>78</v>
+      </c>
+      <c r="E102">
+        <v>57</v>
+      </c>
+      <c r="F102">
+        <v>0.7308</v>
+      </c>
+      <c r="G102">
+        <v>0.1458</v>
+      </c>
+      <c r="H102">
+        <v>64</v>
+      </c>
+      <c r="I102">
+        <v>35</v>
+      </c>
+      <c r="J102">
+        <v>0.5469000000000001</v>
+      </c>
+      <c r="K102">
+        <v>0.0456</v>
+      </c>
+      <c r="L102">
+        <v>20</v>
+      </c>
+      <c r="M102">
+        <v>8</v>
+      </c>
+      <c r="N102">
+        <v>0.4</v>
+      </c>
+      <c r="O102">
+        <v>0.1959</v>
+      </c>
+      <c r="P102">
+        <v>86</v>
+      </c>
+      <c r="Q102">
+        <v>25</v>
+      </c>
+      <c r="R102">
+        <v>0.2907</v>
+      </c>
+      <c r="S102">
+        <v>0.4351</v>
+      </c>
+      <c r="T102">
+        <v>191</v>
+      </c>
+      <c r="U102">
+        <v>68</v>
+      </c>
+      <c r="V102">
+        <v>0.356</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22">
+      <c r="A103" t="s">
+        <v>123</v>
+      </c>
+      <c r="B103">
+        <v>478</v>
+      </c>
+      <c r="C103">
+        <v>0.2678</v>
+      </c>
+      <c r="D103">
+        <v>128</v>
+      </c>
+      <c r="E103">
+        <v>71</v>
+      </c>
+      <c r="F103">
+        <v>0.5547</v>
+      </c>
+      <c r="G103">
+        <v>0.1297</v>
+      </c>
+      <c r="H103">
+        <v>62</v>
+      </c>
+      <c r="I103">
+        <v>21</v>
+      </c>
+      <c r="J103">
+        <v>0.3387</v>
+      </c>
+      <c r="K103">
+        <v>0.0586</v>
+      </c>
+      <c r="L103">
+        <v>28</v>
+      </c>
+      <c r="M103">
+        <v>11</v>
+      </c>
+      <c r="N103">
+        <v>0.3929</v>
+      </c>
+      <c r="O103">
+        <v>0.1757</v>
+      </c>
+      <c r="P103">
+        <v>84</v>
+      </c>
+      <c r="Q103">
+        <v>28</v>
+      </c>
+      <c r="R103">
+        <v>0.3333</v>
+      </c>
+      <c r="S103">
+        <v>0.3682</v>
+      </c>
+      <c r="T103">
+        <v>176</v>
+      </c>
+      <c r="U103">
+        <v>52</v>
+      </c>
+      <c r="V103">
+        <v>0.2955</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22">
+      <c r="A104" t="s">
+        <v>124</v>
+      </c>
+      <c r="B104">
+        <v>601</v>
+      </c>
+      <c r="C104">
+        <v>0.0466</v>
+      </c>
+      <c r="D104">
+        <v>28</v>
+      </c>
+      <c r="E104">
+        <v>23</v>
+      </c>
+      <c r="F104">
+        <v>0.8214</v>
+      </c>
+      <c r="G104">
+        <v>0.0433</v>
+      </c>
+      <c r="H104">
+        <v>26</v>
+      </c>
+      <c r="I104">
+        <v>11</v>
+      </c>
+      <c r="J104">
+        <v>0.4231</v>
+      </c>
+      <c r="K104">
+        <v>0.0732</v>
+      </c>
+      <c r="L104">
+        <v>44</v>
+      </c>
+      <c r="M104">
+        <v>21</v>
+      </c>
+      <c r="N104">
+        <v>0.4773</v>
+      </c>
+      <c r="O104">
+        <v>0.1597</v>
+      </c>
+      <c r="P104">
+        <v>96</v>
+      </c>
+      <c r="Q104">
+        <v>43</v>
+      </c>
+      <c r="R104">
+        <v>0.4479</v>
+      </c>
+      <c r="S104">
+        <v>0.6772</v>
+      </c>
+      <c r="T104">
+        <v>407</v>
+      </c>
+      <c r="U104">
+        <v>154</v>
+      </c>
+      <c r="V104">
+        <v>0.3784</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22">
+      <c r="A105" t="s">
+        <v>125</v>
+      </c>
+      <c r="B105">
+        <v>18</v>
+      </c>
+      <c r="C105">
+        <v>0.8889</v>
+      </c>
+      <c r="D105">
+        <v>16</v>
+      </c>
+      <c r="E105">
+        <v>10</v>
+      </c>
+      <c r="F105">
+        <v>0.625</v>
+      </c>
+      <c r="G105">
+        <v>0.1111</v>
+      </c>
+      <c r="H105">
+        <v>2</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0.5</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>0</v>
+      </c>
+      <c r="R105">
+        <v>0</v>
+      </c>
+      <c r="S105">
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105">
+        <v>0</v>
+      </c>
+      <c r="V105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22">
+      <c r="A106" t="s">
+        <v>126</v>
+      </c>
+      <c r="B106">
+        <v>262</v>
+      </c>
+      <c r="C106">
+        <v>0.3168</v>
+      </c>
+      <c r="D106">
+        <v>83</v>
+      </c>
+      <c r="E106">
+        <v>56</v>
+      </c>
+      <c r="F106">
+        <v>0.6747</v>
+      </c>
+      <c r="G106">
+        <v>0.1183</v>
+      </c>
+      <c r="H106">
+        <v>31</v>
+      </c>
+      <c r="I106">
+        <v>17</v>
+      </c>
+      <c r="J106">
+        <v>0.5484</v>
+      </c>
+      <c r="K106">
+        <v>0.0153</v>
+      </c>
+      <c r="L106">
+        <v>4</v>
+      </c>
+      <c r="M106">
+        <v>2</v>
+      </c>
+      <c r="N106">
+        <v>0.5</v>
+      </c>
+      <c r="O106">
+        <v>0.3511</v>
+      </c>
+      <c r="P106">
+        <v>92</v>
+      </c>
+      <c r="Q106">
+        <v>34</v>
+      </c>
+      <c r="R106">
+        <v>0.3696</v>
+      </c>
+      <c r="S106">
+        <v>0.1985</v>
+      </c>
+      <c r="T106">
+        <v>52</v>
+      </c>
+      <c r="U106">
+        <v>23</v>
+      </c>
+      <c r="V106">
+        <v>0.4423</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22">
+      <c r="A107" t="s">
+        <v>127</v>
+      </c>
+      <c r="B107">
+        <v>362</v>
+      </c>
+      <c r="C107">
+        <v>0.3757</v>
+      </c>
+      <c r="D107">
+        <v>136</v>
+      </c>
+      <c r="E107">
+        <v>89</v>
+      </c>
+      <c r="F107">
+        <v>0.6544</v>
+      </c>
+      <c r="G107">
+        <v>0.1381</v>
+      </c>
+      <c r="H107">
+        <v>50</v>
+      </c>
+      <c r="I107">
+        <v>18</v>
+      </c>
+      <c r="J107">
+        <v>0.36</v>
+      </c>
+      <c r="K107">
+        <v>0.0193</v>
+      </c>
+      <c r="L107">
+        <v>7</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>0.1429</v>
+      </c>
+      <c r="O107">
+        <v>0.3287</v>
+      </c>
+      <c r="P107">
+        <v>119</v>
+      </c>
+      <c r="Q107">
+        <v>43</v>
+      </c>
+      <c r="R107">
+        <v>0.3613</v>
+      </c>
+      <c r="S107">
+        <v>0.1381</v>
+      </c>
+      <c r="T107">
+        <v>50</v>
+      </c>
+      <c r="U107">
+        <v>13</v>
+      </c>
+      <c r="V107">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22">
+      <c r="A108" t="s">
+        <v>128</v>
+      </c>
+      <c r="B108">
+        <v>438</v>
+      </c>
+      <c r="C108">
+        <v>0.7055</v>
+      </c>
+      <c r="D108">
+        <v>309</v>
+      </c>
+      <c r="E108">
+        <v>222</v>
+      </c>
+      <c r="F108">
+        <v>0.7184</v>
+      </c>
+      <c r="G108">
+        <v>0.2648</v>
+      </c>
+      <c r="H108">
+        <v>116</v>
+      </c>
+      <c r="I108">
+        <v>53</v>
+      </c>
+      <c r="J108">
+        <v>0.4569</v>
+      </c>
+      <c r="K108">
+        <v>0.0274</v>
+      </c>
+      <c r="L108">
+        <v>12</v>
+      </c>
+      <c r="M108">
+        <v>6</v>
+      </c>
+      <c r="N108">
+        <v>0.5</v>
+      </c>
+      <c r="O108">
+        <v>0.0023</v>
+      </c>
+      <c r="P108">
+        <v>1</v>
+      </c>
+      <c r="Q108">
+        <v>1</v>
+      </c>
+      <c r="R108">
+        <v>1</v>
+      </c>
+      <c r="S108">
+        <v>0</v>
+      </c>
+      <c r="T108">
+        <v>0</v>
+      </c>
+      <c r="U108">
+        <v>0</v>
+      </c>
+      <c r="V108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22">
+      <c r="A109" t="s">
+        <v>129</v>
+      </c>
+      <c r="B109">
+        <v>342</v>
+      </c>
+      <c r="C109">
+        <v>0.6784</v>
+      </c>
+      <c r="D109">
+        <v>232</v>
+      </c>
+      <c r="E109">
+        <v>161</v>
+      </c>
+      <c r="F109">
+        <v>0.694</v>
+      </c>
+      <c r="G109">
+        <v>0.114</v>
+      </c>
+      <c r="H109">
+        <v>39</v>
+      </c>
+      <c r="I109">
+        <v>15</v>
+      </c>
+      <c r="J109">
+        <v>0.3846</v>
+      </c>
+      <c r="K109">
+        <v>0.0614</v>
+      </c>
+      <c r="L109">
+        <v>21</v>
+      </c>
+      <c r="M109">
+        <v>5</v>
+      </c>
+      <c r="N109">
+        <v>0.2381</v>
+      </c>
+      <c r="O109">
+        <v>0.0439</v>
+      </c>
+      <c r="P109">
+        <v>15</v>
+      </c>
+      <c r="Q109">
+        <v>3</v>
+      </c>
+      <c r="R109">
+        <v>0.2</v>
+      </c>
+      <c r="S109">
+        <v>0.1023</v>
+      </c>
+      <c r="T109">
+        <v>35</v>
+      </c>
+      <c r="U109">
+        <v>14</v>
+      </c>
+      <c r="V109">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22">
+      <c r="A110" t="s">
+        <v>130</v>
+      </c>
+      <c r="B110">
+        <v>536</v>
+      </c>
+      <c r="C110">
+        <v>0.2817</v>
+      </c>
+      <c r="D110">
+        <v>151</v>
+      </c>
+      <c r="E110">
+        <v>91</v>
+      </c>
+      <c r="F110">
+        <v>0.6026</v>
+      </c>
+      <c r="G110">
+        <v>0.1679</v>
+      </c>
+      <c r="H110">
+        <v>90</v>
+      </c>
+      <c r="I110">
+        <v>35</v>
+      </c>
+      <c r="J110">
+        <v>0.3889</v>
+      </c>
+      <c r="K110">
+        <v>0.0466</v>
+      </c>
+      <c r="L110">
+        <v>25</v>
+      </c>
+      <c r="M110">
+        <v>9</v>
+      </c>
+      <c r="N110">
+        <v>0.36</v>
+      </c>
+      <c r="O110">
+        <v>0.1567</v>
+      </c>
+      <c r="P110">
+        <v>84</v>
+      </c>
+      <c r="Q110">
+        <v>31</v>
+      </c>
+      <c r="R110">
+        <v>0.369</v>
+      </c>
+      <c r="S110">
+        <v>0.347</v>
+      </c>
+      <c r="T110">
+        <v>186</v>
+      </c>
+      <c r="U110">
+        <v>65</v>
+      </c>
+      <c r="V110">
+        <v>0.3495</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22">
+      <c r="A111" t="s">
+        <v>131</v>
+      </c>
+      <c r="B111">
+        <v>657</v>
+      </c>
+      <c r="C111">
+        <v>0.3425</v>
+      </c>
+      <c r="D111">
+        <v>225</v>
+      </c>
+      <c r="E111">
+        <v>155</v>
+      </c>
+      <c r="F111">
+        <v>0.6889</v>
+      </c>
+      <c r="G111">
+        <v>0.2816</v>
+      </c>
+      <c r="H111">
+        <v>185</v>
+      </c>
+      <c r="I111">
+        <v>88</v>
+      </c>
+      <c r="J111">
+        <v>0.4757</v>
+      </c>
+      <c r="K111">
+        <v>0.0289</v>
+      </c>
+      <c r="L111">
+        <v>19</v>
+      </c>
+      <c r="M111">
+        <v>6</v>
+      </c>
+      <c r="N111">
+        <v>0.3158</v>
+      </c>
+      <c r="O111">
+        <v>0.1492</v>
+      </c>
+      <c r="P111">
+        <v>98</v>
+      </c>
+      <c r="Q111">
+        <v>33</v>
+      </c>
+      <c r="R111">
+        <v>0.3367</v>
+      </c>
+      <c r="S111">
+        <v>0.1979</v>
+      </c>
+      <c r="T111">
+        <v>130</v>
+      </c>
+      <c r="U111">
+        <v>41</v>
+      </c>
+      <c r="V111">
+        <v>0.3154</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22">
+      <c r="A112" t="s">
+        <v>132</v>
+      </c>
+      <c r="B112">
+        <v>881</v>
+      </c>
+      <c r="C112">
+        <v>0.1532</v>
+      </c>
+      <c r="D112">
+        <v>135</v>
+      </c>
+      <c r="E112">
+        <v>97</v>
+      </c>
+      <c r="F112">
+        <v>0.7185</v>
+      </c>
+      <c r="G112">
+        <v>0.2736</v>
+      </c>
+      <c r="H112">
+        <v>241</v>
+      </c>
+      <c r="I112">
+        <v>111</v>
+      </c>
+      <c r="J112">
+        <v>0.4606</v>
+      </c>
+      <c r="K112">
+        <v>0.1623</v>
+      </c>
+      <c r="L112">
+        <v>143</v>
+      </c>
+      <c r="M112">
+        <v>60</v>
+      </c>
+      <c r="N112">
+        <v>0.4196</v>
+      </c>
+      <c r="O112">
+        <v>0.0545</v>
+      </c>
+      <c r="P112">
+        <v>48</v>
+      </c>
+      <c r="Q112">
+        <v>19</v>
+      </c>
+      <c r="R112">
+        <v>0.3958</v>
+      </c>
+      <c r="S112">
+        <v>0.3564</v>
+      </c>
+      <c r="T112">
+        <v>314</v>
+      </c>
+      <c r="U112">
+        <v>115</v>
+      </c>
+      <c r="V112">
+        <v>0.3662</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22">
+      <c r="A113" t="s">
+        <v>133</v>
+      </c>
+      <c r="B113">
+        <v>1501</v>
+      </c>
+      <c r="C113">
+        <v>0.2838</v>
+      </c>
+      <c r="D113">
+        <v>426</v>
+      </c>
+      <c r="E113">
+        <v>274</v>
+      </c>
+      <c r="F113">
+        <v>0.6432</v>
+      </c>
+      <c r="G113">
+        <v>0.1959</v>
+      </c>
+      <c r="H113">
+        <v>294</v>
+      </c>
+      <c r="I113">
+        <v>120</v>
+      </c>
+      <c r="J113">
+        <v>0.4082</v>
+      </c>
+      <c r="K113">
+        <v>0.1206</v>
+      </c>
+      <c r="L113">
+        <v>181</v>
+      </c>
+      <c r="M113">
+        <v>79</v>
+      </c>
+      <c r="N113">
+        <v>0.4365</v>
+      </c>
+      <c r="O113">
+        <v>0.0333</v>
+      </c>
+      <c r="P113">
+        <v>50</v>
+      </c>
+      <c r="Q113">
+        <v>17</v>
+      </c>
+      <c r="R113">
+        <v>0.34</v>
+      </c>
+      <c r="S113">
+        <v>0.3664</v>
+      </c>
+      <c r="T113">
+        <v>550</v>
+      </c>
+      <c r="U113">
+        <v>204</v>
+      </c>
+      <c r="V113">
+        <v>0.3709</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22">
+      <c r="A114" t="s">
+        <v>134</v>
+      </c>
+      <c r="B114">
+        <v>611</v>
+      </c>
+      <c r="C114">
+        <v>0.2962</v>
+      </c>
+      <c r="D114">
+        <v>181</v>
+      </c>
+      <c r="E114">
+        <v>137</v>
+      </c>
+      <c r="F114">
+        <v>0.7569</v>
+      </c>
+      <c r="G114">
+        <v>0.08019999999999999</v>
+      </c>
+      <c r="H114">
+        <v>49</v>
+      </c>
+      <c r="I114">
+        <v>29</v>
+      </c>
+      <c r="J114">
+        <v>0.5918</v>
+      </c>
+      <c r="K114">
+        <v>0.0131</v>
+      </c>
+      <c r="L114">
+        <v>8</v>
+      </c>
+      <c r="M114">
+        <v>6</v>
+      </c>
+      <c r="N114">
+        <v>0.75</v>
+      </c>
+      <c r="O114">
+        <v>0.0786</v>
+      </c>
+      <c r="P114">
+        <v>48</v>
+      </c>
+      <c r="Q114">
+        <v>13</v>
+      </c>
+      <c r="R114">
+        <v>0.2708</v>
+      </c>
+      <c r="S114">
+        <v>0.5319</v>
+      </c>
+      <c r="T114">
+        <v>325</v>
+      </c>
+      <c r="U114">
+        <v>106</v>
+      </c>
+      <c r="V114">
+        <v>0.3262</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22">
+      <c r="A115" t="s">
+        <v>135</v>
+      </c>
+      <c r="B115">
+        <v>1123</v>
+      </c>
+      <c r="C115">
+        <v>0.1852</v>
+      </c>
+      <c r="D115">
+        <v>208</v>
+      </c>
+      <c r="E115">
+        <v>133</v>
+      </c>
+      <c r="F115">
+        <v>0.6394</v>
+      </c>
+      <c r="G115">
+        <v>0.2182</v>
+      </c>
+      <c r="H115">
+        <v>245</v>
+      </c>
+      <c r="I115">
+        <v>100</v>
+      </c>
+      <c r="J115">
+        <v>0.4082</v>
+      </c>
+      <c r="K115">
+        <v>0.0864</v>
+      </c>
+      <c r="L115">
+        <v>97</v>
+      </c>
+      <c r="M115">
+        <v>39</v>
+      </c>
+      <c r="N115">
+        <v>0.4021</v>
+      </c>
+      <c r="O115">
+        <v>0.0285</v>
+      </c>
+      <c r="P115">
+        <v>32</v>
+      </c>
+      <c r="Q115">
+        <v>10</v>
+      </c>
+      <c r="R115">
+        <v>0.3125</v>
+      </c>
+      <c r="S115">
+        <v>0.4817</v>
+      </c>
+      <c r="T115">
+        <v>541</v>
+      </c>
+      <c r="U115">
+        <v>205</v>
+      </c>
+      <c r="V115">
+        <v>0.3789</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22">
+      <c r="A116" t="s">
+        <v>136</v>
+      </c>
+      <c r="B116">
+        <v>296</v>
+      </c>
+      <c r="C116">
+        <v>0.3176</v>
+      </c>
+      <c r="D116">
+        <v>94</v>
+      </c>
+      <c r="E116">
+        <v>59</v>
+      </c>
+      <c r="F116">
+        <v>0.6277</v>
+      </c>
+      <c r="G116">
+        <v>0.1351</v>
+      </c>
+      <c r="H116">
+        <v>40</v>
+      </c>
+      <c r="I116">
+        <v>15</v>
+      </c>
+      <c r="J116">
+        <v>0.375</v>
+      </c>
+      <c r="K116">
+        <v>0.1115</v>
+      </c>
+      <c r="L116">
+        <v>33</v>
+      </c>
+      <c r="M116">
+        <v>16</v>
+      </c>
+      <c r="N116">
+        <v>0.4848</v>
+      </c>
+      <c r="O116">
+        <v>0.1115</v>
+      </c>
+      <c r="P116">
+        <v>33</v>
+      </c>
+      <c r="Q116">
+        <v>15</v>
+      </c>
+      <c r="R116">
+        <v>0.4545</v>
+      </c>
+      <c r="S116">
+        <v>0.3243</v>
+      </c>
+      <c r="T116">
+        <v>96</v>
+      </c>
+      <c r="U116">
+        <v>35</v>
+      </c>
+      <c r="V116">
+        <v>0.3646</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22">
+      <c r="A117" t="s">
+        <v>137</v>
+      </c>
+      <c r="B117">
+        <v>821</v>
+      </c>
+      <c r="C117">
+        <v>0.2753</v>
+      </c>
+      <c r="D117">
+        <v>226</v>
+      </c>
+      <c r="E117">
+        <v>161</v>
+      </c>
+      <c r="F117">
+        <v>0.7124</v>
+      </c>
+      <c r="G117">
+        <v>0.3922</v>
+      </c>
+      <c r="H117">
+        <v>322</v>
+      </c>
+      <c r="I117">
+        <v>174</v>
+      </c>
+      <c r="J117">
+        <v>0.5404</v>
+      </c>
+      <c r="K117">
+        <v>0.0731</v>
+      </c>
+      <c r="L117">
+        <v>60</v>
+      </c>
+      <c r="M117">
+        <v>22</v>
+      </c>
+      <c r="N117">
+        <v>0.3667</v>
+      </c>
+      <c r="O117">
+        <v>0.1255</v>
+      </c>
+      <c r="P117">
+        <v>103</v>
+      </c>
+      <c r="Q117">
+        <v>36</v>
+      </c>
+      <c r="R117">
+        <v>0.3495</v>
+      </c>
+      <c r="S117">
+        <v>0.134</v>
+      </c>
+      <c r="T117">
+        <v>110</v>
+      </c>
+      <c r="U117">
+        <v>26</v>
+      </c>
+      <c r="V117">
+        <v>0.2364</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22">
+      <c r="A118" t="s">
+        <v>138</v>
+      </c>
+      <c r="B118">
+        <v>292</v>
+      </c>
+      <c r="C118">
+        <v>0.137</v>
+      </c>
+      <c r="D118">
+        <v>40</v>
+      </c>
+      <c r="E118">
+        <v>16</v>
+      </c>
+      <c r="F118">
+        <v>0.4</v>
+      </c>
+      <c r="G118">
+        <v>0.1986</v>
+      </c>
+      <c r="H118">
+        <v>58</v>
+      </c>
+      <c r="I118">
+        <v>25</v>
+      </c>
+      <c r="J118">
+        <v>0.431</v>
+      </c>
+      <c r="K118">
+        <v>0.0582</v>
+      </c>
+      <c r="L118">
+        <v>17</v>
+      </c>
+      <c r="M118">
+        <v>7</v>
+      </c>
+      <c r="N118">
+        <v>0.4118</v>
+      </c>
+      <c r="O118">
+        <v>0.1164</v>
+      </c>
+      <c r="P118">
+        <v>34</v>
+      </c>
+      <c r="Q118">
+        <v>12</v>
+      </c>
+      <c r="R118">
+        <v>0.3529</v>
+      </c>
+      <c r="S118">
+        <v>0.4897</v>
+      </c>
+      <c r="T118">
+        <v>143</v>
+      </c>
+      <c r="U118">
+        <v>43</v>
+      </c>
+      <c r="V118">
+        <v>0.3007</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22">
+      <c r="A119" t="s">
+        <v>139</v>
+      </c>
+      <c r="B119">
+        <v>333</v>
+      </c>
+      <c r="C119">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="D119">
+        <v>28</v>
+      </c>
+      <c r="E119">
+        <v>20</v>
+      </c>
+      <c r="F119">
+        <v>0.7143</v>
+      </c>
+      <c r="G119">
+        <v>0.1171</v>
+      </c>
+      <c r="H119">
+        <v>39</v>
+      </c>
+      <c r="I119">
+        <v>21</v>
+      </c>
+      <c r="J119">
+        <v>0.5385</v>
+      </c>
+      <c r="K119">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="L119">
+        <v>23</v>
+      </c>
+      <c r="M119">
+        <v>13</v>
+      </c>
+      <c r="N119">
+        <v>0.5652</v>
+      </c>
+      <c r="O119">
+        <v>0.2643</v>
+      </c>
+      <c r="P119">
+        <v>88</v>
+      </c>
+      <c r="Q119">
+        <v>42</v>
+      </c>
+      <c r="R119">
+        <v>0.4773</v>
+      </c>
+      <c r="S119">
+        <v>0.4655</v>
+      </c>
+      <c r="T119">
+        <v>155</v>
+      </c>
+      <c r="U119">
+        <v>55</v>
+      </c>
+      <c r="V119">
+        <v>0.3548</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22">
+      <c r="A120" t="s">
+        <v>140</v>
+      </c>
+      <c r="B120">
+        <v>748</v>
+      </c>
+      <c r="C120">
+        <v>0.5</v>
+      </c>
+      <c r="D120">
+        <v>374</v>
+      </c>
+      <c r="E120">
+        <v>226</v>
+      </c>
+      <c r="F120">
+        <v>0.6042999999999999</v>
+      </c>
+      <c r="G120">
+        <v>0.2634</v>
+      </c>
+      <c r="H120">
+        <v>197</v>
+      </c>
+      <c r="I120">
+        <v>74</v>
+      </c>
+      <c r="J120">
+        <v>0.3756</v>
+      </c>
+      <c r="K120">
+        <v>0.119</v>
+      </c>
+      <c r="L120">
+        <v>89</v>
+      </c>
+      <c r="M120">
+        <v>31</v>
+      </c>
+      <c r="N120">
+        <v>0.3483</v>
+      </c>
+      <c r="O120">
+        <v>0.0414</v>
+      </c>
+      <c r="P120">
+        <v>31</v>
+      </c>
+      <c r="Q120">
+        <v>9</v>
+      </c>
+      <c r="R120">
+        <v>0.2903</v>
+      </c>
+      <c r="S120">
+        <v>0.0762</v>
+      </c>
+      <c r="T120">
+        <v>57</v>
+      </c>
+      <c r="U120">
+        <v>14</v>
+      </c>
+      <c r="V120">
+        <v>0.2456</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22">
+      <c r="A121" t="s">
+        <v>141</v>
+      </c>
+      <c r="B121">
+        <v>123</v>
+      </c>
+      <c r="C121">
+        <v>0.3415</v>
+      </c>
+      <c r="D121">
+        <v>42</v>
+      </c>
+      <c r="E121">
+        <v>26</v>
+      </c>
+      <c r="F121">
+        <v>0.619</v>
+      </c>
+      <c r="G121">
+        <v>0.122</v>
+      </c>
+      <c r="H121">
+        <v>15</v>
+      </c>
+      <c r="I121">
+        <v>7</v>
+      </c>
+      <c r="J121">
+        <v>0.4667</v>
+      </c>
+      <c r="K121">
+        <v>0.0163</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0.1545</v>
+      </c>
+      <c r="P121">
+        <v>19</v>
+      </c>
+      <c r="Q121">
+        <v>5</v>
+      </c>
+      <c r="R121">
+        <v>0.2632</v>
+      </c>
+      <c r="S121">
+        <v>0.3659</v>
+      </c>
+      <c r="T121">
+        <v>45</v>
+      </c>
+      <c r="U121">
+        <v>21</v>
+      </c>
+      <c r="V121">
+        <v>0.4667</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22">
+      <c r="A122" t="s">
+        <v>142</v>
+      </c>
+      <c r="B122">
+        <v>276</v>
+      </c>
+      <c r="C122">
+        <v>0.4891</v>
+      </c>
+      <c r="D122">
+        <v>135</v>
+      </c>
+      <c r="E122">
+        <v>88</v>
+      </c>
+      <c r="F122">
+        <v>0.6519</v>
+      </c>
+      <c r="G122">
+        <v>0.0688</v>
+      </c>
+      <c r="H122">
+        <v>19</v>
+      </c>
+      <c r="I122">
+        <v>7</v>
+      </c>
+      <c r="J122">
+        <v>0.3684</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0.2572</v>
+      </c>
+      <c r="P122">
+        <v>71</v>
+      </c>
+      <c r="Q122">
+        <v>20</v>
+      </c>
+      <c r="R122">
+        <v>0.2817</v>
+      </c>
+      <c r="S122">
+        <v>0.1848</v>
+      </c>
+      <c r="T122">
+        <v>51</v>
+      </c>
+      <c r="U122">
+        <v>14</v>
+      </c>
+      <c r="V122">
+        <v>0.2745</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22">
+      <c r="A123" t="s">
+        <v>143</v>
+      </c>
+      <c r="B123">
+        <v>860</v>
+      </c>
+      <c r="C123">
+        <v>0.2791</v>
+      </c>
+      <c r="D123">
+        <v>240</v>
+      </c>
+      <c r="E123">
+        <v>163</v>
+      </c>
+      <c r="F123">
+        <v>0.6792</v>
+      </c>
+      <c r="G123">
+        <v>0.2663</v>
+      </c>
+      <c r="H123">
+        <v>229</v>
+      </c>
+      <c r="I123">
+        <v>103</v>
+      </c>
+      <c r="J123">
+        <v>0.4498</v>
+      </c>
+      <c r="K123">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="L123">
+        <v>8</v>
+      </c>
+      <c r="M123">
+        <v>3</v>
+      </c>
+      <c r="N123">
+        <v>0.375</v>
+      </c>
+      <c r="O123">
+        <v>0.1244</v>
+      </c>
+      <c r="P123">
+        <v>107</v>
+      </c>
+      <c r="Q123">
+        <v>42</v>
+      </c>
+      <c r="R123">
+        <v>0.3925</v>
+      </c>
+      <c r="S123">
+        <v>0.3209</v>
+      </c>
+      <c r="T123">
+        <v>276</v>
+      </c>
+      <c r="U123">
+        <v>102</v>
+      </c>
+      <c r="V123">
+        <v>0.3696</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22">
+      <c r="A124" t="s">
+        <v>144</v>
+      </c>
+      <c r="B124">
+        <v>698</v>
+      </c>
+      <c r="C124">
+        <v>0.1862</v>
+      </c>
+      <c r="D124">
+        <v>130</v>
+      </c>
+      <c r="E124">
+        <v>76</v>
+      </c>
+      <c r="F124">
+        <v>0.5846</v>
+      </c>
+      <c r="G124">
+        <v>0.1461</v>
+      </c>
+      <c r="H124">
+        <v>102</v>
+      </c>
+      <c r="I124">
+        <v>48</v>
+      </c>
+      <c r="J124">
+        <v>0.4706</v>
+      </c>
+      <c r="K124">
+        <v>0.1447</v>
+      </c>
+      <c r="L124">
+        <v>101</v>
+      </c>
+      <c r="M124">
+        <v>48</v>
+      </c>
+      <c r="N124">
+        <v>0.4752</v>
+      </c>
+      <c r="O124">
+        <v>0.1862</v>
+      </c>
+      <c r="P124">
+        <v>130</v>
+      </c>
+      <c r="Q124">
+        <v>47</v>
+      </c>
+      <c r="R124">
+        <v>0.3615</v>
+      </c>
+      <c r="S124">
+        <v>0.3367</v>
+      </c>
+      <c r="T124">
+        <v>235</v>
+      </c>
+      <c r="U124">
+        <v>82</v>
+      </c>
+      <c r="V124">
+        <v>0.3489</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22">
+      <c r="A125" t="s">
+        <v>145</v>
+      </c>
+      <c r="B125">
+        <v>779</v>
+      </c>
+      <c r="C125">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="D125">
+        <v>76</v>
+      </c>
+      <c r="E125">
+        <v>48</v>
+      </c>
+      <c r="F125">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="G125">
+        <v>0.0822</v>
+      </c>
+      <c r="H125">
+        <v>64</v>
+      </c>
+      <c r="I125">
+        <v>28</v>
+      </c>
+      <c r="J125">
+        <v>0.4375</v>
+      </c>
+      <c r="K125">
+        <v>0.1142</v>
+      </c>
+      <c r="L125">
+        <v>89</v>
+      </c>
+      <c r="M125">
+        <v>48</v>
+      </c>
+      <c r="N125">
+        <v>0.5393</v>
+      </c>
+      <c r="O125">
+        <v>0.1451</v>
+      </c>
+      <c r="P125">
+        <v>113</v>
+      </c>
+      <c r="Q125">
+        <v>49</v>
+      </c>
+      <c r="R125">
+        <v>0.4336</v>
+      </c>
+      <c r="S125">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="T125">
+        <v>437</v>
+      </c>
+      <c r="U125">
+        <v>175</v>
+      </c>
+      <c r="V125">
+        <v>0.4005</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22">
+      <c r="A126" t="s">
+        <v>146</v>
+      </c>
+      <c r="B126">
+        <v>177</v>
+      </c>
+      <c r="C126">
+        <v>0.1356</v>
+      </c>
+      <c r="D126">
+        <v>24</v>
+      </c>
+      <c r="E126">
+        <v>13</v>
+      </c>
+      <c r="F126">
+        <v>0.5417</v>
+      </c>
+      <c r="G126">
+        <v>0.1412</v>
+      </c>
+      <c r="H126">
+        <v>25</v>
+      </c>
+      <c r="I126">
+        <v>7</v>
+      </c>
+      <c r="J126">
+        <v>0.28</v>
+      </c>
+      <c r="K126">
+        <v>0.1243</v>
+      </c>
+      <c r="L126">
+        <v>22</v>
+      </c>
+      <c r="M126">
+        <v>5</v>
+      </c>
+      <c r="N126">
+        <v>0.2273</v>
+      </c>
+      <c r="O126">
+        <v>0.1582</v>
+      </c>
+      <c r="P126">
+        <v>28</v>
+      </c>
+      <c r="Q126">
+        <v>17</v>
+      </c>
+      <c r="R126">
+        <v>0.6071</v>
+      </c>
+      <c r="S126">
+        <v>0.4407</v>
+      </c>
+      <c r="T126">
+        <v>78</v>
+      </c>
+      <c r="U126">
+        <v>27</v>
+      </c>
+      <c r="V126">
+        <v>0.3462</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22">
+      <c r="A127" t="s">
+        <v>147</v>
+      </c>
+      <c r="B127">
+        <v>857</v>
+      </c>
+      <c r="C127">
+        <v>0.1575</v>
+      </c>
+      <c r="D127">
+        <v>135</v>
+      </c>
+      <c r="E127">
+        <v>94</v>
+      </c>
+      <c r="F127">
+        <v>0.6963</v>
+      </c>
+      <c r="G127">
+        <v>0.2264</v>
+      </c>
+      <c r="H127">
+        <v>194</v>
+      </c>
+      <c r="I127">
+        <v>101</v>
+      </c>
+      <c r="J127">
+        <v>0.5206</v>
+      </c>
+      <c r="K127">
+        <v>0.1004</v>
+      </c>
+      <c r="L127">
+        <v>86</v>
+      </c>
+      <c r="M127">
+        <v>37</v>
+      </c>
+      <c r="N127">
+        <v>0.4302</v>
+      </c>
+      <c r="O127">
+        <v>0.126</v>
+      </c>
+      <c r="P127">
+        <v>108</v>
+      </c>
+      <c r="Q127">
+        <v>51</v>
+      </c>
+      <c r="R127">
+        <v>0.4722</v>
+      </c>
+      <c r="S127">
+        <v>0.3897</v>
+      </c>
+      <c r="T127">
+        <v>334</v>
+      </c>
+      <c r="U127">
+        <v>111</v>
+      </c>
+      <c r="V127">
+        <v>0.3323</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22">
+      <c r="A128" t="s">
+        <v>148</v>
+      </c>
+      <c r="B128">
+        <v>429</v>
+      </c>
+      <c r="C128">
+        <v>0.1026</v>
+      </c>
+      <c r="D128">
+        <v>44</v>
+      </c>
+      <c r="E128">
+        <v>32</v>
+      </c>
+      <c r="F128">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="G128">
+        <v>0.1026</v>
+      </c>
+      <c r="H128">
+        <v>44</v>
+      </c>
+      <c r="I128">
+        <v>25</v>
+      </c>
+      <c r="J128">
+        <v>0.5682</v>
+      </c>
+      <c r="K128">
+        <v>0.0303</v>
+      </c>
+      <c r="L128">
+        <v>13</v>
+      </c>
+      <c r="M128">
+        <v>7</v>
+      </c>
+      <c r="N128">
+        <v>0.5385</v>
+      </c>
+      <c r="O128">
+        <v>0.1958</v>
+      </c>
+      <c r="P128">
+        <v>84</v>
+      </c>
+      <c r="Q128">
+        <v>31</v>
+      </c>
+      <c r="R128">
+        <v>0.369</v>
+      </c>
+      <c r="S128">
+        <v>0.5688</v>
+      </c>
+      <c r="T128">
+        <v>244</v>
+      </c>
+      <c r="U128">
+        <v>97</v>
+      </c>
+      <c r="V128">
+        <v>0.3975</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22">
+      <c r="A129" t="s">
+        <v>149</v>
+      </c>
+      <c r="B129">
+        <v>206</v>
+      </c>
+      <c r="C129">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="D129">
+        <v>203</v>
+      </c>
+      <c r="E129">
+        <v>146</v>
+      </c>
+      <c r="F129">
+        <v>0.7192</v>
+      </c>
+      <c r="G129">
+        <v>0.0146</v>
+      </c>
+      <c r="H129">
+        <v>3</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>0</v>
+      </c>
+      <c r="R129">
+        <v>0</v>
+      </c>
+      <c r="S129">
+        <v>0</v>
+      </c>
+      <c r="T129">
+        <v>0</v>
+      </c>
+      <c r="U129">
+        <v>0</v>
+      </c>
+      <c r="V129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22">
+      <c r="A130" t="s">
+        <v>150</v>
+      </c>
+      <c r="B130">
+        <v>314</v>
+      </c>
+      <c r="C130">
+        <v>0.5255</v>
+      </c>
+      <c r="D130">
+        <v>165</v>
+      </c>
+      <c r="E130">
+        <v>110</v>
+      </c>
+      <c r="F130">
+        <v>0.6667</v>
+      </c>
+      <c r="G130">
+        <v>0.1083</v>
+      </c>
+      <c r="H130">
+        <v>34</v>
+      </c>
+      <c r="I130">
+        <v>13</v>
+      </c>
+      <c r="J130">
+        <v>0.3824</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0.2325</v>
+      </c>
+      <c r="P130">
+        <v>73</v>
+      </c>
+      <c r="Q130">
+        <v>17</v>
+      </c>
+      <c r="R130">
+        <v>0.2329</v>
+      </c>
+      <c r="S130">
+        <v>0.1338</v>
+      </c>
+      <c r="T130">
+        <v>42</v>
+      </c>
+      <c r="U130">
+        <v>10</v>
+      </c>
+      <c r="V130">
+        <v>0.2381</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22">
+      <c r="A131" t="s">
+        <v>151</v>
+      </c>
+      <c r="B131">
+        <v>25</v>
+      </c>
+      <c r="C131">
+        <v>0.28</v>
+      </c>
+      <c r="D131">
+        <v>7</v>
+      </c>
+      <c r="E131">
+        <v>5</v>
+      </c>
+      <c r="F131">
+        <v>0.7143</v>
+      </c>
+      <c r="G131">
+        <v>0.08</v>
+      </c>
+      <c r="H131">
+        <v>2</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>0.5</v>
+      </c>
+      <c r="K131">
+        <v>0.04</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0.12</v>
+      </c>
+      <c r="P131">
+        <v>3</v>
+      </c>
+      <c r="Q131">
+        <v>0</v>
+      </c>
+      <c r="R131">
+        <v>0</v>
+      </c>
+      <c r="S131">
+        <v>0.48</v>
+      </c>
+      <c r="T131">
+        <v>12</v>
+      </c>
+      <c r="U131">
+        <v>2</v>
+      </c>
+      <c r="V131">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22">
+      <c r="A132" t="s">
+        <v>152</v>
+      </c>
+      <c r="B132">
+        <v>101</v>
+      </c>
+      <c r="C132">
+        <v>0.8416</v>
+      </c>
+      <c r="D132">
+        <v>85</v>
+      </c>
+      <c r="E132">
+        <v>59</v>
+      </c>
+      <c r="F132">
+        <v>0.6941000000000001</v>
+      </c>
+      <c r="G132">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="H132">
+        <v>8</v>
+      </c>
+      <c r="I132">
+        <v>3</v>
+      </c>
+      <c r="J132">
+        <v>0.375</v>
+      </c>
+      <c r="K132">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132">
+        <v>0.0495</v>
+      </c>
+      <c r="P132">
+        <v>5</v>
+      </c>
+      <c r="Q132">
+        <v>2</v>
+      </c>
+      <c r="R132">
+        <v>0.4</v>
+      </c>
+      <c r="S132">
+        <v>0.0198</v>
+      </c>
+      <c r="T132">
+        <v>2</v>
+      </c>
+      <c r="U132">
+        <v>0</v>
+      </c>
+      <c r="V132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22">
+      <c r="A133" t="s">
+        <v>153</v>
+      </c>
+      <c r="B133">
+        <v>220</v>
+      </c>
+      <c r="C133">
+        <v>0.8364</v>
+      </c>
+      <c r="D133">
+        <v>184</v>
+      </c>
+      <c r="E133">
+        <v>118</v>
+      </c>
+      <c r="F133">
+        <v>0.6413</v>
+      </c>
+      <c r="G133">
+        <v>0.1318</v>
+      </c>
+      <c r="H133">
+        <v>29</v>
+      </c>
+      <c r="I133">
+        <v>11</v>
+      </c>
+      <c r="J133">
+        <v>0.3793</v>
+      </c>
+      <c r="K133">
+        <v>0.0045</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0.0227</v>
+      </c>
+      <c r="P133">
+        <v>5</v>
+      </c>
+      <c r="Q133">
+        <v>1</v>
+      </c>
+      <c r="R133">
+        <v>0.2</v>
+      </c>
+      <c r="S133">
+        <v>0.0045</v>
+      </c>
+      <c r="T133">
+        <v>1</v>
+      </c>
+      <c r="U133">
+        <v>1</v>
+      </c>
+      <c r="V133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22">
+      <c r="A134" t="s">
+        <v>154</v>
+      </c>
+      <c r="B134">
+        <v>292</v>
+      </c>
+      <c r="C134">
+        <v>0.3014</v>
+      </c>
+      <c r="D134">
+        <v>88</v>
+      </c>
+      <c r="E134">
+        <v>55</v>
+      </c>
+      <c r="F134">
+        <v>0.625</v>
+      </c>
+      <c r="G134">
+        <v>0.2705</v>
+      </c>
+      <c r="H134">
+        <v>79</v>
+      </c>
+      <c r="I134">
+        <v>34</v>
+      </c>
+      <c r="J134">
+        <v>0.4304</v>
+      </c>
+      <c r="K134">
+        <v>0.0377</v>
+      </c>
+      <c r="L134">
+        <v>11</v>
+      </c>
+      <c r="M134">
+        <v>2</v>
+      </c>
+      <c r="N134">
+        <v>0.1818</v>
+      </c>
+      <c r="O134">
+        <v>0.0411</v>
+      </c>
+      <c r="P134">
+        <v>12</v>
+      </c>
+      <c r="Q134">
+        <v>4</v>
+      </c>
+      <c r="R134">
+        <v>0.3333</v>
+      </c>
+      <c r="S134">
+        <v>0.3493</v>
+      </c>
+      <c r="T134">
+        <v>102</v>
+      </c>
+      <c r="U134">
+        <v>26</v>
+      </c>
+      <c r="V134">
+        <v>0.2549</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22">
+      <c r="A135" t="s">
+        <v>155</v>
+      </c>
+      <c r="B135">
+        <v>325</v>
+      </c>
+      <c r="C135">
+        <v>0.2954</v>
+      </c>
+      <c r="D135">
+        <v>96</v>
+      </c>
+      <c r="E135">
+        <v>57</v>
+      </c>
+      <c r="F135">
+        <v>0.5938</v>
+      </c>
+      <c r="G135">
+        <v>0.2708</v>
+      </c>
+      <c r="H135">
+        <v>88</v>
+      </c>
+      <c r="I135">
+        <v>33</v>
+      </c>
+      <c r="J135">
+        <v>0.375</v>
+      </c>
+      <c r="K135">
+        <v>0.0369</v>
+      </c>
+      <c r="L135">
+        <v>12</v>
+      </c>
+      <c r="M135">
+        <v>7</v>
+      </c>
+      <c r="N135">
+        <v>0.5833</v>
+      </c>
+      <c r="O135">
+        <v>0.1538</v>
+      </c>
+      <c r="P135">
+        <v>50</v>
+      </c>
+      <c r="Q135">
+        <v>15</v>
+      </c>
+      <c r="R135">
+        <v>0.3</v>
+      </c>
+      <c r="S135">
+        <v>0.2431</v>
+      </c>
+      <c r="T135">
+        <v>79</v>
+      </c>
+      <c r="U135">
+        <v>23</v>
+      </c>
+      <c r="V135">
+        <v>0.2911</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22">
+      <c r="A136" t="s">
+        <v>156</v>
+      </c>
+      <c r="B136">
+        <v>346</v>
+      </c>
+      <c r="C136">
+        <v>0.2746</v>
+      </c>
+      <c r="D136">
+        <v>95</v>
+      </c>
+      <c r="E136">
+        <v>75</v>
+      </c>
+      <c r="F136">
+        <v>0.7895</v>
+      </c>
+      <c r="G136">
+        <v>0.078</v>
+      </c>
+      <c r="H136">
+        <v>27</v>
+      </c>
+      <c r="I136">
+        <v>10</v>
+      </c>
+      <c r="J136">
+        <v>0.3704</v>
+      </c>
+      <c r="K136">
+        <v>0.0347</v>
+      </c>
+      <c r="L136">
+        <v>12</v>
+      </c>
+      <c r="M136">
+        <v>6</v>
+      </c>
+      <c r="N136">
+        <v>0.5</v>
+      </c>
+      <c r="O136">
+        <v>0.2832</v>
+      </c>
+      <c r="P136">
+        <v>98</v>
+      </c>
+      <c r="Q136">
+        <v>36</v>
+      </c>
+      <c r="R136">
+        <v>0.3673</v>
+      </c>
+      <c r="S136">
+        <v>0.3295</v>
+      </c>
+      <c r="T136">
+        <v>114</v>
+      </c>
+      <c r="U136">
+        <v>35</v>
+      </c>
+      <c r="V136">
+        <v>0.307</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22">
+      <c r="A137" t="s">
+        <v>157</v>
+      </c>
+      <c r="B137">
+        <v>544</v>
+      </c>
+      <c r="C137">
+        <v>0.2702</v>
+      </c>
+      <c r="D137">
+        <v>147</v>
+      </c>
+      <c r="E137">
+        <v>98</v>
+      </c>
+      <c r="F137">
+        <v>0.6667</v>
+      </c>
+      <c r="G137">
+        <v>0.2408</v>
+      </c>
+      <c r="H137">
+        <v>131</v>
+      </c>
+      <c r="I137">
+        <v>61</v>
+      </c>
+      <c r="J137">
+        <v>0.4656</v>
+      </c>
+      <c r="K137">
+        <v>0.0496</v>
+      </c>
+      <c r="L137">
+        <v>27</v>
+      </c>
+      <c r="M137">
+        <v>9</v>
+      </c>
+      <c r="N137">
+        <v>0.3333</v>
+      </c>
+      <c r="O137">
+        <v>0.1599</v>
+      </c>
+      <c r="P137">
+        <v>87</v>
+      </c>
+      <c r="Q137">
+        <v>40</v>
+      </c>
+      <c r="R137">
+        <v>0.4598</v>
+      </c>
+      <c r="S137">
+        <v>0.2794</v>
+      </c>
+      <c r="T137">
+        <v>152</v>
+      </c>
+      <c r="U137">
+        <v>46</v>
+      </c>
+      <c r="V137">
+        <v>0.3026</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22">
+      <c r="A138" t="s">
+        <v>158</v>
+      </c>
+      <c r="B138">
+        <v>533</v>
+      </c>
+      <c r="C138">
+        <v>0.2627</v>
+      </c>
+      <c r="D138">
+        <v>140</v>
+      </c>
+      <c r="E138">
+        <v>90</v>
+      </c>
+      <c r="F138">
+        <v>0.6429</v>
+      </c>
+      <c r="G138">
+        <v>0.242</v>
+      </c>
+      <c r="H138">
+        <v>129</v>
+      </c>
+      <c r="I138">
+        <v>67</v>
+      </c>
+      <c r="J138">
+        <v>0.5194</v>
+      </c>
+      <c r="K138">
+        <v>0.0675</v>
+      </c>
+      <c r="L138">
+        <v>36</v>
+      </c>
+      <c r="M138">
+        <v>14</v>
+      </c>
+      <c r="N138">
+        <v>0.3889</v>
+      </c>
+      <c r="O138">
+        <v>0.0544</v>
+      </c>
+      <c r="P138">
+        <v>29</v>
+      </c>
+      <c r="Q138">
+        <v>8</v>
+      </c>
+      <c r="R138">
+        <v>0.2759</v>
+      </c>
+      <c r="S138">
+        <v>0.3734</v>
+      </c>
+      <c r="T138">
+        <v>199</v>
+      </c>
+      <c r="U138">
+        <v>82</v>
+      </c>
+      <c r="V138">
+        <v>0.4121</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22">
+      <c r="A139" t="s">
+        <v>159</v>
+      </c>
+      <c r="B139">
+        <v>278</v>
+      </c>
+      <c r="C139">
+        <v>0.2302</v>
+      </c>
+      <c r="D139">
+        <v>64</v>
+      </c>
+      <c r="E139">
+        <v>41</v>
+      </c>
+      <c r="F139">
+        <v>0.6405999999999999</v>
+      </c>
+      <c r="G139">
+        <v>0.036</v>
+      </c>
+      <c r="H139">
+        <v>10</v>
+      </c>
+      <c r="I139">
+        <v>7</v>
+      </c>
+      <c r="J139">
+        <v>0.7</v>
+      </c>
+      <c r="K139">
+        <v>0.0288</v>
+      </c>
+      <c r="L139">
+        <v>8</v>
+      </c>
+      <c r="M139">
+        <v>3</v>
+      </c>
+      <c r="N139">
+        <v>0.375</v>
+      </c>
+      <c r="O139">
+        <v>0.2842</v>
+      </c>
+      <c r="P139">
+        <v>79</v>
+      </c>
+      <c r="Q139">
+        <v>31</v>
+      </c>
+      <c r="R139">
+        <v>0.3924</v>
+      </c>
+      <c r="S139">
+        <v>0.4209</v>
+      </c>
+      <c r="T139">
+        <v>117</v>
+      </c>
+      <c r="U139">
+        <v>40</v>
+      </c>
+      <c r="V139">
+        <v>0.3419</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22">
+      <c r="A140" t="s">
+        <v>160</v>
+      </c>
+      <c r="B140">
+        <v>362</v>
+      </c>
+      <c r="C140">
+        <v>0.1768</v>
+      </c>
+      <c r="D140">
+        <v>64</v>
+      </c>
+      <c r="E140">
+        <v>45</v>
+      </c>
+      <c r="F140">
+        <v>0.7030999999999999</v>
+      </c>
+      <c r="G140">
+        <v>0.1188</v>
+      </c>
+      <c r="H140">
+        <v>43</v>
+      </c>
+      <c r="I140">
+        <v>23</v>
+      </c>
+      <c r="J140">
+        <v>0.5349</v>
+      </c>
+      <c r="K140">
+        <v>0.0414</v>
+      </c>
+      <c r="L140">
+        <v>15</v>
+      </c>
+      <c r="M140">
+        <v>7</v>
+      </c>
+      <c r="N140">
+        <v>0.4667</v>
+      </c>
+      <c r="O140">
+        <v>0.2818</v>
+      </c>
+      <c r="P140">
+        <v>102</v>
+      </c>
+      <c r="Q140">
+        <v>46</v>
+      </c>
+      <c r="R140">
+        <v>0.451</v>
+      </c>
+      <c r="S140">
+        <v>0.3812</v>
+      </c>
+      <c r="T140">
+        <v>138</v>
+      </c>
+      <c r="U140">
+        <v>52</v>
+      </c>
+      <c r="V140">
+        <v>0.3768</v>
+      </c>
+    </row>
+    <row r="141" spans="1:22">
+      <c r="A141" t="s">
+        <v>161</v>
+      </c>
+      <c r="B141">
+        <v>568</v>
+      </c>
+      <c r="C141">
+        <v>0.2377</v>
+      </c>
+      <c r="D141">
+        <v>135</v>
+      </c>
+      <c r="E141">
+        <v>77</v>
+      </c>
+      <c r="F141">
+        <v>0.5704</v>
+      </c>
+      <c r="G141">
+        <v>0.2465</v>
+      </c>
+      <c r="H141">
+        <v>140</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>0.3</v>
+      </c>
+      <c r="K141">
+        <v>0.1725</v>
+      </c>
+      <c r="L141">
+        <v>98</v>
+      </c>
+      <c r="M141">
+        <v>40</v>
+      </c>
+      <c r="N141">
+        <v>0.4082</v>
+      </c>
+      <c r="O141">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="P141">
+        <v>50</v>
+      </c>
+      <c r="Q141">
+        <v>20</v>
+      </c>
+      <c r="R141">
+        <v>0.4</v>
+      </c>
+      <c r="S141">
+        <v>0.2535</v>
+      </c>
+      <c r="T141">
+        <v>144</v>
+      </c>
+      <c r="U141">
+        <v>52</v>
+      </c>
+      <c r="V141">
+        <v>0.3611</v>
+      </c>
+    </row>
+    <row r="142" spans="1:22">
+      <c r="A142" t="s">
+        <v>162</v>
+      </c>
+      <c r="B142">
+        <v>258</v>
+      </c>
+      <c r="C142">
+        <v>0.2868</v>
+      </c>
+      <c r="D142">
+        <v>74</v>
+      </c>
+      <c r="E142">
+        <v>51</v>
+      </c>
+      <c r="F142">
+        <v>0.6892</v>
+      </c>
+      <c r="G142">
+        <v>0.2868</v>
+      </c>
+      <c r="H142">
+        <v>74</v>
+      </c>
+      <c r="I142">
+        <v>23</v>
+      </c>
+      <c r="J142">
+        <v>0.3108</v>
+      </c>
+      <c r="K142">
+        <v>0.0659</v>
+      </c>
+      <c r="L142">
+        <v>17</v>
+      </c>
+      <c r="M142">
+        <v>9</v>
+      </c>
+      <c r="N142">
+        <v>0.5294</v>
+      </c>
+      <c r="O142">
+        <v>0.1318</v>
+      </c>
+      <c r="P142">
+        <v>34</v>
+      </c>
+      <c r="Q142">
+        <v>14</v>
+      </c>
+      <c r="R142">
+        <v>0.4118</v>
+      </c>
+      <c r="S142">
+        <v>0.2287</v>
+      </c>
+      <c r="T142">
+        <v>59</v>
+      </c>
+      <c r="U142">
+        <v>19</v>
+      </c>
+      <c r="V142">
+        <v>0.322</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22">
+      <c r="A143" t="s">
+        <v>163</v>
+      </c>
+      <c r="B143">
+        <v>1194</v>
+      </c>
+      <c r="C143">
+        <v>0.2764</v>
+      </c>
+      <c r="D143">
+        <v>330</v>
+      </c>
+      <c r="E143">
+        <v>217</v>
+      </c>
+      <c r="F143">
+        <v>0.6576</v>
+      </c>
+      <c r="G143">
+        <v>0.3157</v>
+      </c>
+      <c r="H143">
+        <v>377</v>
+      </c>
+      <c r="I143">
+        <v>178</v>
+      </c>
+      <c r="J143">
+        <v>0.4721</v>
+      </c>
+      <c r="K143">
+        <v>0.2027</v>
+      </c>
+      <c r="L143">
+        <v>242</v>
+      </c>
+      <c r="M143">
+        <v>92</v>
+      </c>
+      <c r="N143">
+        <v>0.3802</v>
+      </c>
+      <c r="O143">
+        <v>0.0268</v>
+      </c>
+      <c r="P143">
+        <v>32</v>
+      </c>
+      <c r="Q143">
+        <v>8</v>
+      </c>
+      <c r="R143">
+        <v>0.25</v>
+      </c>
+      <c r="S143">
+        <v>0.1784</v>
+      </c>
+      <c r="T143">
+        <v>213</v>
+      </c>
+      <c r="U143">
+        <v>64</v>
+      </c>
+      <c r="V143">
+        <v>0.3005</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22">
+      <c r="A144" t="s">
+        <v>164</v>
+      </c>
+      <c r="B144">
+        <v>399</v>
+      </c>
+      <c r="C144">
+        <v>0.5714</v>
+      </c>
+      <c r="D144">
+        <v>228</v>
+      </c>
+      <c r="E144">
+        <v>163</v>
+      </c>
+      <c r="F144">
+        <v>0.7149</v>
+      </c>
+      <c r="G144">
+        <v>0.1905</v>
+      </c>
+      <c r="H144">
+        <v>76</v>
+      </c>
+      <c r="I144">
+        <v>28</v>
+      </c>
+      <c r="J144">
+        <v>0.3684</v>
+      </c>
+      <c r="K144">
+        <v>0.0351</v>
+      </c>
+      <c r="L144">
+        <v>14</v>
+      </c>
+      <c r="M144">
+        <v>3</v>
+      </c>
+      <c r="N144">
+        <v>0.2143</v>
+      </c>
+      <c r="O144">
+        <v>0.1629</v>
+      </c>
+      <c r="P144">
+        <v>65</v>
+      </c>
+      <c r="Q144">
+        <v>16</v>
+      </c>
+      <c r="R144">
+        <v>0.2462</v>
+      </c>
+      <c r="S144">
+        <v>0.0401</v>
+      </c>
+      <c r="T144">
+        <v>16</v>
+      </c>
+      <c r="U144">
+        <v>5</v>
+      </c>
+      <c r="V144">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="145" spans="1:22">
+      <c r="A145" t="s">
+        <v>165</v>
+      </c>
+      <c r="B145">
+        <v>149</v>
+      </c>
+      <c r="C145">
+        <v>0.4161</v>
+      </c>
+      <c r="D145">
+        <v>62</v>
+      </c>
+      <c r="E145">
+        <v>43</v>
+      </c>
+      <c r="F145">
+        <v>0.6935</v>
+      </c>
+      <c r="G145">
+        <v>0.0872</v>
+      </c>
+      <c r="H145">
+        <v>13</v>
+      </c>
+      <c r="I145">
+        <v>4</v>
+      </c>
+      <c r="J145">
+        <v>0.3077</v>
+      </c>
+      <c r="K145">
+        <v>0.0201</v>
+      </c>
+      <c r="L145">
+        <v>3</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0.2013</v>
+      </c>
+      <c r="P145">
+        <v>30</v>
+      </c>
+      <c r="Q145">
+        <v>10</v>
+      </c>
+      <c r="R145">
+        <v>0.3333</v>
+      </c>
+      <c r="S145">
+        <v>0.2752</v>
+      </c>
+      <c r="T145">
+        <v>41</v>
+      </c>
+      <c r="U145">
+        <v>13</v>
+      </c>
+      <c r="V145">
+        <v>0.3171</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22">
+      <c r="A146" t="s">
+        <v>166</v>
+      </c>
+      <c r="B146">
+        <v>350</v>
+      </c>
+      <c r="C146">
+        <v>0.4314</v>
+      </c>
+      <c r="D146">
+        <v>151</v>
+      </c>
+      <c r="E146">
+        <v>111</v>
+      </c>
+      <c r="F146">
+        <v>0.7351</v>
+      </c>
+      <c r="G146">
+        <v>0.1257</v>
+      </c>
+      <c r="H146">
+        <v>44</v>
+      </c>
+      <c r="I146">
+        <v>19</v>
+      </c>
+      <c r="J146">
+        <v>0.4318</v>
+      </c>
+      <c r="K146">
+        <v>0.02</v>
+      </c>
+      <c r="L146">
+        <v>7</v>
+      </c>
+      <c r="M146">
+        <v>2</v>
+      </c>
+      <c r="N146">
+        <v>0.2857</v>
+      </c>
+      <c r="O146">
+        <v>0.16</v>
+      </c>
+      <c r="P146">
+        <v>56</v>
+      </c>
+      <c r="Q146">
+        <v>21</v>
+      </c>
+      <c r="R146">
+        <v>0.375</v>
+      </c>
+      <c r="S146">
+        <v>0.2629</v>
+      </c>
+      <c r="T146">
+        <v>92</v>
+      </c>
+      <c r="U146">
+        <v>39</v>
+      </c>
+      <c r="V146">
+        <v>0.4239</v>
+      </c>
+    </row>
+    <row r="147" spans="1:22">
+      <c r="A147" t="s">
+        <v>167</v>
+      </c>
+      <c r="B147">
+        <v>262</v>
+      </c>
+      <c r="C147">
+        <v>0.8015</v>
+      </c>
+      <c r="D147">
+        <v>210</v>
+      </c>
+      <c r="E147">
+        <v>165</v>
+      </c>
+      <c r="F147">
+        <v>0.7857</v>
+      </c>
+      <c r="G147">
+        <v>0.187</v>
+      </c>
+      <c r="H147">
+        <v>49</v>
+      </c>
+      <c r="I147">
+        <v>30</v>
+      </c>
+      <c r="J147">
+        <v>0.6122</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>0</v>
+      </c>
+      <c r="R147">
+        <v>0</v>
+      </c>
+      <c r="S147">
+        <v>0.0115</v>
+      </c>
+      <c r="T147">
+        <v>3</v>
+      </c>
+      <c r="U147">
+        <v>3</v>
+      </c>
+      <c r="V147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:22">
+      <c r="A148" t="s">
+        <v>168</v>
+      </c>
+      <c r="B148">
+        <v>543</v>
+      </c>
+      <c r="C148">
+        <v>0.0921</v>
+      </c>
+      <c r="D148">
+        <v>50</v>
+      </c>
+      <c r="E148">
+        <v>31</v>
+      </c>
+      <c r="F148">
+        <v>0.62</v>
+      </c>
+      <c r="G148">
+        <v>0.0497</v>
+      </c>
+      <c r="H148">
+        <v>27</v>
+      </c>
+      <c r="I148">
+        <v>16</v>
+      </c>
+      <c r="J148">
+        <v>0.5926</v>
+      </c>
+      <c r="K148">
+        <v>0.0718</v>
+      </c>
+      <c r="L148">
+        <v>39</v>
+      </c>
+      <c r="M148">
+        <v>19</v>
+      </c>
+      <c r="N148">
+        <v>0.4872</v>
+      </c>
+      <c r="O148">
+        <v>0.186</v>
+      </c>
+      <c r="P148">
+        <v>101</v>
+      </c>
+      <c r="Q148">
+        <v>54</v>
+      </c>
+      <c r="R148">
+        <v>0.5347</v>
+      </c>
+      <c r="S148">
+        <v>0.6004</v>
+      </c>
+      <c r="T148">
+        <v>326</v>
+      </c>
+      <c r="U148">
+        <v>127</v>
+      </c>
+      <c r="V148">
+        <v>0.3896</v>
+      </c>
+    </row>
+    <row r="149" spans="1:22">
+      <c r="A149" t="s">
+        <v>169</v>
+      </c>
+      <c r="B149">
+        <v>213</v>
+      </c>
+      <c r="C149">
+        <v>0.4648</v>
+      </c>
+      <c r="D149">
+        <v>99</v>
+      </c>
+      <c r="E149">
+        <v>61</v>
+      </c>
+      <c r="F149">
+        <v>0.6162</v>
+      </c>
+      <c r="G149">
+        <v>0.0751</v>
+      </c>
+      <c r="H149">
+        <v>16</v>
+      </c>
+      <c r="I149">
+        <v>3</v>
+      </c>
+      <c r="J149">
+        <v>0.1875</v>
+      </c>
+      <c r="K149">
+        <v>0.0141</v>
+      </c>
+      <c r="L149">
+        <v>3</v>
+      </c>
+      <c r="M149">
+        <v>1</v>
+      </c>
+      <c r="N149">
+        <v>0.3333</v>
+      </c>
+      <c r="O149">
+        <v>0.2488</v>
+      </c>
+      <c r="P149">
+        <v>53</v>
+      </c>
+      <c r="Q149">
+        <v>21</v>
+      </c>
+      <c r="R149">
+        <v>0.3962</v>
+      </c>
+      <c r="S149">
+        <v>0.1972</v>
+      </c>
+      <c r="T149">
+        <v>42</v>
+      </c>
+      <c r="U149">
+        <v>11</v>
+      </c>
+      <c r="V149">
+        <v>0.2619</v>
+      </c>
+    </row>
+    <row r="150" spans="1:22">
+      <c r="A150" t="s">
+        <v>170</v>
+      </c>
+      <c r="B150">
+        <v>725</v>
+      </c>
+      <c r="C150">
+        <v>0.1724</v>
+      </c>
+      <c r="D150">
+        <v>125</v>
+      </c>
+      <c r="E150">
+        <v>82</v>
+      </c>
+      <c r="F150">
+        <v>0.656</v>
+      </c>
+      <c r="G150">
+        <v>0.1379</v>
+      </c>
+      <c r="H150">
+        <v>100</v>
+      </c>
+      <c r="I150">
+        <v>37</v>
+      </c>
+      <c r="J150">
+        <v>0.37</v>
+      </c>
+      <c r="K150">
+        <v>0.0745</v>
+      </c>
+      <c r="L150">
+        <v>54</v>
+      </c>
+      <c r="M150">
+        <v>21</v>
+      </c>
+      <c r="N150">
+        <v>0.3889</v>
+      </c>
+      <c r="O150">
+        <v>0.2276</v>
+      </c>
+      <c r="P150">
+        <v>165</v>
+      </c>
+      <c r="Q150">
+        <v>75</v>
+      </c>
+      <c r="R150">
+        <v>0.4545</v>
+      </c>
+      <c r="S150">
+        <v>0.3876</v>
+      </c>
+      <c r="T150">
+        <v>281</v>
+      </c>
+      <c r="U150">
+        <v>105</v>
+      </c>
+      <c r="V150">
+        <v>0.3737</v>
+      </c>
+    </row>
+    <row r="151" spans="1:22">
+      <c r="A151" t="s">
+        <v>171</v>
+      </c>
+      <c r="B151">
+        <v>291</v>
+      </c>
+      <c r="C151">
+        <v>0.8385</v>
+      </c>
+      <c r="D151">
+        <v>244</v>
+      </c>
+      <c r="E151">
+        <v>195</v>
+      </c>
+      <c r="F151">
+        <v>0.7992</v>
+      </c>
+      <c r="G151">
+        <v>0.1306</v>
+      </c>
+      <c r="H151">
+        <v>38</v>
+      </c>
+      <c r="I151">
+        <v>23</v>
+      </c>
+      <c r="J151">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="K151">
+        <v>0.0137</v>
+      </c>
+      <c r="L151">
+        <v>4</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>0.25</v>
+      </c>
+      <c r="O151">
+        <v>0.0034</v>
+      </c>
+      <c r="P151">
+        <v>1</v>
+      </c>
+      <c r="Q151">
+        <v>0</v>
+      </c>
+      <c r="R151">
+        <v>0</v>
+      </c>
+      <c r="S151">
+        <v>0.0137</v>
+      </c>
+      <c r="T151">
+        <v>4</v>
+      </c>
+      <c r="U151">
+        <v>0</v>
+      </c>
+      <c r="V151">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
